--- a/ig/nr-update-patient-ins/StructureDefinition-fr-core-patient.xlsx
+++ b/ig/nr-update-patient-ins/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-26T11:00:29+00:00</t>
+    <t>2024-02-26T11:04:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-update-patient-ins/StructureDefinition-fr-core-patient.xlsx
+++ b/ig/nr-update-patient-ins/StructureDefinition-fr-core-patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5004" uniqueCount="680">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5341" uniqueCount="692">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0</t>
+    <t>2.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-26T11:04:56+00:00</t>
+    <t>2024-02-26T11:06:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1001,13 +1001,63 @@
     <t>CX.4 / (CX.4,CX.9,CX.10)</t>
   </si>
   <si>
+    <t>Patient.identifier:NSS</t>
+  </si>
+  <si>
+    <t>NSS</t>
+  </si>
+  <si>
+    <t>National Health Plan Identifier | Le Numéro d'Inscription au Répertoire (NIR) de facturation permet de faire transiter le numéro de sécurité social de l’ayant droit ou du bénéfiaire (patient) / le numéro de sécurité sociale de l’ouvrant droit (assuré).</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS.id</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS.extension</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS.use</t>
+  </si>
+  <si>
+    <t>official</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS.type</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://terminology.hl7.org/CodeSystem/v2-0203"/&gt;
+    &lt;code value="NH"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS.system</t>
+  </si>
+  <si>
+    <t>urn:oid:1.2.250.1.213.1.4.8</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS.value</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS.period</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS.assigner</t>
+  </si>
+  <si>
     <t>Patient.identifier:INS-C</t>
   </si>
   <si>
     <t>INS-C</t>
-  </si>
-  <si>
-    <t>An identifier for this patient</t>
   </si>
   <si>
     <t>Computed National Health Identifier | Identifiant National de Santé Calculé à partir des éléments de la carte vitale</t>
@@ -1037,12 +1087,6 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
-  </si>
-  <si>
     <t>Patient.identifier:INS-C.system</t>
   </si>
   <si>
@@ -1501,9 +1545,6 @@
   </si>
   <si>
     <t>Patient.name:officialName.use</t>
-  </si>
-  <si>
-    <t>official</t>
   </si>
   <si>
     <t>Patient.name:officialName.text</t>
@@ -2461,7 +2502,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO133"/>
+  <dimension ref="A1:AO142"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="54.79296875" customWidth="true" bestFit="true"/>
@@ -6859,7 +6900,7 @@
         <v>79</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>81</v>
@@ -6877,7 +6918,7 @@
         <v>318</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>319</v>
+        <v>252</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
@@ -6962,7 +7003,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>260</v>
@@ -7077,7 +7118,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>261</v>
@@ -7194,7 +7235,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>262</v>
@@ -7242,7 +7283,7 @@
         <v>81</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="T41" t="s" s="2">
         <v>81</v>
@@ -7313,7 +7354,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>272</v>
@@ -7345,7 +7386,7 @@
         <v>274</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>319</v>
+        <v>275</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>276</v>
@@ -7361,7 +7402,7 @@
         <v>81</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>81</v>
@@ -7379,10 +7420,10 @@
         <v>153</v>
       </c>
       <c r="Y42" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="Z42" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="Z42" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>81</v>
@@ -7432,7 +7473,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>281</v>
@@ -7480,7 +7521,7 @@
         <v>81</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>286</v>
@@ -7551,7 +7592,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>290</v>
@@ -7668,7 +7709,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>298</v>
@@ -7785,7 +7826,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>307</v>
@@ -7902,13 +7943,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>249</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>81</v>
@@ -7918,7 +7959,7 @@
         <v>79</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>81</v>
@@ -7933,7 +7974,7 @@
         <v>250</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="M47" t="s" s="2">
         <v>252</v>
@@ -8021,7 +8062,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>260</v>
@@ -8136,7 +8177,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>261</v>
@@ -8253,7 +8294,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>262</v>
@@ -8301,7 +8342,7 @@
         <v>81</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="T50" t="s" s="2">
         <v>81</v>
@@ -8404,7 +8445,7 @@
         <v>274</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>275</v>
+        <v>334</v>
       </c>
       <c r="N51" t="s" s="2">
         <v>276</v>
@@ -8437,9 +8478,11 @@
       <c r="X51" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="Y51" s="2"/>
+      <c r="Y51" t="s" s="2">
+        <v>325</v>
+      </c>
       <c r="Z51" t="s" s="2">
-        <v>278</v>
+        <v>326</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>81</v>
@@ -8500,7 +8543,7 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>89</v>
@@ -8993,7 +9036,7 @@
         <v>348</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>348</v>
+        <v>252</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
@@ -9358,7 +9401,7 @@
         <v>81</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>352</v>
+        <v>338</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>81</v>
@@ -9429,7 +9472,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>272</v>
@@ -9477,7 +9520,7 @@
         <v>81</v>
       </c>
       <c r="S60" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="T60" t="s" s="2">
         <v>81</v>
@@ -9495,10 +9538,10 @@
         <v>153</v>
       </c>
       <c r="Y60" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="Z60" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="Z60" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>81</v>
@@ -9548,7 +9591,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>281</v>
@@ -9596,7 +9639,7 @@
         <v>81</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>81</v>
+        <v>355</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>286</v>
@@ -10034,7 +10077,7 @@
         <v>79</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>81</v>
@@ -10052,7 +10095,7 @@
         <v>361</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>361</v>
+        <v>252</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
@@ -10417,7 +10460,7 @@
         <v>81</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>323</v>
+        <v>365</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>81</v>
@@ -10488,7 +10531,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B69" t="s" s="2">
         <v>272</v>
@@ -10536,7 +10579,7 @@
         <v>81</v>
       </c>
       <c r="S69" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="T69" t="s" s="2">
         <v>81</v>
@@ -10554,10 +10597,10 @@
         <v>153</v>
       </c>
       <c r="Y69" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="Z69" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>81</v>
@@ -10607,7 +10650,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>281</v>
@@ -10726,7 +10769,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>290</v>
@@ -10843,7 +10886,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>298</v>
@@ -10960,7 +11003,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B73" t="s" s="2">
         <v>307</v>
@@ -11077,12 +11120,14 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="C74" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="C74" t="s" s="2">
+        <v>373</v>
+      </c>
       <c r="D74" t="s" s="2">
         <v>81</v>
       </c>
@@ -11091,38 +11136,34 @@
         <v>79</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J74" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>372</v>
+        <v>250</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>375</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>376</v>
+        <v>253</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q74" t="s" s="2">
-        <v>377</v>
-      </c>
+      <c r="Q74" s="2"/>
       <c r="R74" t="s" s="2">
         <v>81</v>
       </c>
@@ -11166,13 +11207,13 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>371</v>
+        <v>249</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>101</v>
@@ -11181,16 +11222,16 @@
         <v>102</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>378</v>
+        <v>256</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>109</v>
+        <v>257</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>379</v>
+        <v>258</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>81</v>
+        <v>259</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>81</v>
@@ -11198,10 +11239,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>380</v>
+        <v>260</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11212,7 +11253,7 @@
         <v>79</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>81</v>
@@ -11221,23 +11262,19 @@
         <v>81</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>381</v>
+        <v>105</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>382</v>
+        <v>106</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>385</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>81</v>
       </c>
@@ -11273,41 +11310,43 @@
         <v>81</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="AC75" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD75" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>380</v>
+        <v>108</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>387</v>
+        <v>109</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>388</v>
+        <v>81</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>389</v>
+        <v>81</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>81</v>
@@ -11315,16 +11354,14 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>390</v>
+        <v>376</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="C76" t="s" s="2">
-        <v>391</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -11340,23 +11377,21 @@
         <v>81</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>392</v>
+        <v>112</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>393</v>
+        <v>113</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>394</v>
+        <v>114</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>385</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>81</v>
       </c>
@@ -11392,19 +11427,19 @@
         <v>81</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>380</v>
+        <v>119</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -11416,19 +11451,19 @@
         <v>101</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>387</v>
+        <v>103</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>388</v>
+        <v>81</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>389</v>
+        <v>81</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>81</v>
@@ -11436,10 +11471,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>395</v>
+        <v>377</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>396</v>
+        <v>262</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11456,22 +11491,26 @@
         <v>81</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>105</v>
+        <v>173</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>106</v>
+        <v>263</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>266</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>81</v>
       </c>
@@ -11480,7 +11519,7 @@
         <v>81</v>
       </c>
       <c r="S77" t="s" s="2">
-        <v>81</v>
+        <v>338</v>
       </c>
       <c r="T77" t="s" s="2">
         <v>81</v>
@@ -11495,13 +11534,13 @@
         <v>81</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>81</v>
+        <v>267</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>81</v>
+        <v>268</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>81</v>
+        <v>269</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>81</v>
@@ -11519,7 +11558,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>108</v>
+        <v>270</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11528,13 +11567,13 @@
         <v>89</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>109</v>
+        <v>271</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>81</v>
@@ -11543,7 +11582,7 @@
         <v>81</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>81</v>
@@ -11551,21 +11590,21 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>397</v>
+        <v>378</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>398</v>
+        <v>272</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>81</v>
@@ -11574,21 +11613,23 @@
         <v>81</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>112</v>
+        <v>273</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>113</v>
+        <v>274</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>114</v>
+        <v>275</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O78" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>277</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>81</v>
       </c>
@@ -11597,7 +11638,7 @@
         <v>81</v>
       </c>
       <c r="S78" t="s" s="2">
-        <v>81</v>
+        <v>379</v>
       </c>
       <c r="T78" t="s" s="2">
         <v>81</v>
@@ -11612,46 +11653,46 @@
         <v>81</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>81</v>
+        <v>153</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>81</v>
+        <v>325</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>81</v>
+        <v>326</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AC78" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AD78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>119</v>
+        <v>279</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>103</v>
+        <v>271</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>81</v>
@@ -11660,7 +11701,7 @@
         <v>81</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>81</v>
+        <v>280</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>81</v>
@@ -11668,10 +11709,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>399</v>
+        <v>380</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>400</v>
+        <v>281</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11688,25 +11729,25 @@
         <v>81</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J79" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>173</v>
+        <v>133</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>401</v>
+        <v>282</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>402</v>
+        <v>283</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>403</v>
+        <v>284</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>404</v>
+        <v>285</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>81</v>
@@ -11716,10 +11757,10 @@
         <v>81</v>
       </c>
       <c r="S79" t="s" s="2">
-        <v>352</v>
+        <v>81</v>
       </c>
       <c r="T79" t="s" s="2">
-        <v>81</v>
+        <v>286</v>
       </c>
       <c r="U79" t="s" s="2">
         <v>81</v>
@@ -11731,13 +11772,13 @@
         <v>81</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>267</v>
+        <v>81</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>405</v>
+        <v>81</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>406</v>
+        <v>81</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>81</v>
@@ -11755,7 +11796,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>407</v>
+        <v>287</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11770,7 +11811,7 @@
         <v>102</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>408</v>
+        <v>288</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>81</v>
@@ -11779,7 +11820,7 @@
         <v>81</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>409</v>
+        <v>289</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>81</v>
@@ -11787,10 +11828,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>410</v>
+        <v>381</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>411</v>
+        <v>290</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11798,7 +11839,7 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G80" t="s" s="2">
         <v>89</v>
@@ -11816,17 +11857,15 @@
         <v>105</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>412</v>
+        <v>291</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>413</v>
+        <v>292</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>415</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>81</v>
       </c>
@@ -11838,7 +11877,7 @@
         <v>81</v>
       </c>
       <c r="T80" t="s" s="2">
-        <v>81</v>
+        <v>294</v>
       </c>
       <c r="U80" t="s" s="2">
         <v>81</v>
@@ -11874,7 +11913,7 @@
         <v>81</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>416</v>
+        <v>295</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11889,7 +11928,7 @@
         <v>102</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>417</v>
+        <v>296</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>81</v>
@@ -11898,7 +11937,7 @@
         <v>81</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>418</v>
+        <v>297</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>81</v>
@@ -11906,14 +11945,14 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>419</v>
+        <v>382</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>420</v>
+        <v>298</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>421</v>
+        <v>81</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -11932,16 +11971,16 @@
         <v>90</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>105</v>
+        <v>299</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>422</v>
+        <v>300</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>423</v>
+        <v>301</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>424</v>
+        <v>302</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11991,7 +12030,7 @@
         <v>81</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>425</v>
+        <v>303</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -12003,10 +12042,10 @@
         <v>101</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>102</v>
+        <v>304</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>426</v>
+        <v>305</v>
       </c>
       <c r="AL81" t="s" s="2">
         <v>81</v>
@@ -12015,7 +12054,7 @@
         <v>81</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>427</v>
+        <v>306</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>81</v>
@@ -12023,21 +12062,21 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>428</v>
+        <v>383</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>429</v>
+        <v>307</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>430</v>
+        <v>81</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>81</v>
@@ -12049,16 +12088,16 @@
         <v>90</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>105</v>
+        <v>308</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>431</v>
+        <v>309</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>432</v>
+        <v>310</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>433</v>
+        <v>311</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12108,22 +12147,22 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>434</v>
+        <v>312</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>102</v>
+        <v>313</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>435</v>
+        <v>314</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>81</v>
@@ -12132,7 +12171,7 @@
         <v>81</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>436</v>
+        <v>315</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>81</v>
@@ -12140,10 +12179,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>437</v>
+        <v>384</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>438</v>
+        <v>384</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12154,34 +12193,38 @@
         <v>79</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J83" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>105</v>
+        <v>385</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>439</v>
+        <v>386</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>440</v>
+        <v>387</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="O83" s="2"/>
+        <v>388</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>389</v>
+      </c>
       <c r="P83" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q83" s="2"/>
+      <c r="Q83" t="s" s="2">
+        <v>390</v>
+      </c>
       <c r="R83" t="s" s="2">
         <v>81</v>
       </c>
@@ -12225,13 +12268,13 @@
         <v>81</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>442</v>
+        <v>384</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>101</v>
@@ -12240,16 +12283,16 @@
         <v>102</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>443</v>
+        <v>391</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>81</v>
+        <v>392</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>444</v>
+        <v>81</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>81</v>
@@ -12257,10 +12300,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>445</v>
+        <v>393</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>446</v>
+        <v>393</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12283,18 +12326,20 @@
         <v>90</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>105</v>
+        <v>394</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>447</v>
+        <v>395</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>448</v>
+        <v>396</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="O84" s="2"/>
+        <v>397</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>398</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>81</v>
       </c>
@@ -12330,19 +12375,17 @@
         <v>81</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="AC84" s="2"/>
       <c r="AD84" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>449</v>
+        <v>393</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -12357,16 +12400,16 @@
         <v>102</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>81</v>
+        <v>401</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>451</v>
+        <v>402</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>81</v>
@@ -12374,12 +12417,14 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>452</v>
+        <v>403</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="C85" s="2"/>
+        <v>393</v>
+      </c>
+      <c r="C85" t="s" s="2">
+        <v>404</v>
+      </c>
       <c r="D85" t="s" s="2">
         <v>81</v>
       </c>
@@ -12388,7 +12433,7 @@
         <v>79</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>81</v>
@@ -12400,19 +12445,19 @@
         <v>90</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>299</v>
+        <v>405</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>454</v>
+        <v>406</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>455</v>
+        <v>407</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>302</v>
+        <v>397</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>456</v>
+        <v>398</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>81</v>
@@ -12461,31 +12506,31 @@
         <v>81</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>457</v>
+        <v>393</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>304</v>
+        <v>102</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>458</v>
+        <v>400</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>81</v>
+        <v>401</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>459</v>
+        <v>402</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>81</v>
@@ -12493,14 +12538,12 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>460</v>
+        <v>408</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="C86" t="s" s="2">
-        <v>461</v>
-      </c>
+        <v>409</v>
+      </c>
+      <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
         <v>81</v>
       </c>
@@ -12509,7 +12552,7 @@
         <v>79</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>81</v>
@@ -12518,23 +12561,19 @@
         <v>81</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>392</v>
+        <v>105</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>462</v>
+        <v>106</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>385</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>81</v>
       </c>
@@ -12582,31 +12621,31 @@
         <v>81</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>380</v>
+        <v>108</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>387</v>
+        <v>109</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>388</v>
+        <v>81</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>389</v>
+        <v>81</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>81</v>
@@ -12614,21 +12653,21 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>464</v>
+        <v>410</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>396</v>
+        <v>411</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>81</v>
@@ -12640,15 +12679,17 @@
         <v>81</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N87" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>81</v>
@@ -12685,34 +12726,34 @@
         <v>81</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AC87" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AD87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="AL87" t="s" s="2">
         <v>81</v>
@@ -12729,44 +12770,46 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>465</v>
+        <v>412</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>398</v>
+        <v>413</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I88" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>112</v>
+        <v>173</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>113</v>
+        <v>414</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>114</v>
+        <v>415</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O88" s="2"/>
+        <v>416</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>417</v>
+      </c>
       <c r="P88" t="s" s="2">
         <v>81</v>
       </c>
@@ -12775,7 +12818,7 @@
         <v>81</v>
       </c>
       <c r="S88" t="s" s="2">
-        <v>81</v>
+        <v>365</v>
       </c>
       <c r="T88" t="s" s="2">
         <v>81</v>
@@ -12790,46 +12833,46 @@
         <v>81</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>81</v>
+        <v>267</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>81</v>
+        <v>418</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>81</v>
+        <v>419</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>119</v>
+        <v>420</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>103</v>
+        <v>421</v>
       </c>
       <c r="AL88" t="s" s="2">
         <v>81</v>
@@ -12838,7 +12881,7 @@
         <v>81</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>81</v>
+        <v>422</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>81</v>
@@ -12846,14 +12889,12 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>466</v>
+        <v>423</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="C89" t="s" s="2">
-        <v>467</v>
-      </c>
+        <v>424</v>
+      </c>
+      <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
         <v>81</v>
       </c>
@@ -12871,19 +12912,23 @@
         <v>81</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>468</v>
+        <v>105</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>469</v>
+        <v>425</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="N89" s="2"/>
-      <c r="O89" s="2"/>
+        <v>426</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>428</v>
+      </c>
       <c r="P89" t="s" s="2">
         <v>81</v>
       </c>
@@ -12931,22 +12976,22 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>119</v>
+        <v>429</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>81</v>
+        <v>430</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>81</v>
@@ -12955,7 +13000,7 @@
         <v>81</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>81</v>
+        <v>431</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>81</v>
@@ -12963,18 +13008,18 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>471</v>
+        <v>432</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>400</v>
+        <v>433</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>81</v>
+        <v>434</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G90" t="s" s="2">
         <v>89</v>
@@ -12983,26 +13028,24 @@
         <v>81</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J90" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>173</v>
+        <v>105</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>401</v>
+        <v>435</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>402</v>
+        <v>436</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>404</v>
-      </c>
+        <v>437</v>
+      </c>
+      <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>81</v>
       </c>
@@ -13011,7 +13054,7 @@
         <v>81</v>
       </c>
       <c r="S90" t="s" s="2">
-        <v>472</v>
+        <v>81</v>
       </c>
       <c r="T90" t="s" s="2">
         <v>81</v>
@@ -13026,13 +13069,13 @@
         <v>81</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>267</v>
+        <v>81</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>405</v>
+        <v>81</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>406</v>
+        <v>81</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>81</v>
@@ -13050,7 +13093,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>407</v>
+        <v>438</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -13065,7 +13108,7 @@
         <v>102</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>408</v>
+        <v>439</v>
       </c>
       <c r="AL90" t="s" s="2">
         <v>81</v>
@@ -13074,7 +13117,7 @@
         <v>81</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>409</v>
+        <v>440</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>81</v>
@@ -13082,21 +13125,21 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>473</v>
+        <v>441</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>411</v>
+        <v>442</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>81</v>
+        <v>443</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>81</v>
@@ -13111,17 +13154,15 @@
         <v>105</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>412</v>
+        <v>444</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>413</v>
+        <v>445</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>415</v>
-      </c>
+        <v>446</v>
+      </c>
+      <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>81</v>
       </c>
@@ -13169,13 +13210,13 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>416</v>
+        <v>447</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>101</v>
@@ -13184,7 +13225,7 @@
         <v>102</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>417</v>
+        <v>448</v>
       </c>
       <c r="AL91" t="s" s="2">
         <v>81</v>
@@ -13193,7 +13234,7 @@
         <v>81</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>418</v>
+        <v>449</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>81</v>
@@ -13201,21 +13242,21 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>474</v>
+        <v>450</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>420</v>
+        <v>451</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>421</v>
+        <v>81</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>81</v>
@@ -13230,13 +13271,13 @@
         <v>105</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>422</v>
+        <v>452</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>423</v>
+        <v>453</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>424</v>
+        <v>454</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13286,13 +13327,13 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>425</v>
+        <v>455</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>101</v>
@@ -13301,7 +13342,7 @@
         <v>102</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>426</v>
+        <v>456</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>81</v>
@@ -13310,7 +13351,7 @@
         <v>81</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>427</v>
+        <v>457</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>81</v>
@@ -13318,18 +13359,18 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>475</v>
+        <v>458</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>429</v>
+        <v>459</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>430</v>
+        <v>81</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G93" t="s" s="2">
         <v>80</v>
@@ -13347,13 +13388,13 @@
         <v>105</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>431</v>
+        <v>460</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>432</v>
+        <v>461</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>433</v>
+        <v>454</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13403,7 +13444,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>434</v>
+        <v>462</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -13418,7 +13459,7 @@
         <v>102</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>435</v>
+        <v>463</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>81</v>
@@ -13427,7 +13468,7 @@
         <v>81</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>436</v>
+        <v>464</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>81</v>
@@ -13435,10 +13476,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>476</v>
+        <v>465</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>438</v>
+        <v>466</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13449,7 +13490,7 @@
         <v>79</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>81</v>
@@ -13461,18 +13502,20 @@
         <v>90</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>105</v>
+        <v>299</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>439</v>
+        <v>467</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>440</v>
+        <v>468</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="O94" s="2"/>
+        <v>302</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>469</v>
+      </c>
       <c r="P94" t="s" s="2">
         <v>81</v>
       </c>
@@ -13520,22 +13563,22 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>442</v>
+        <v>470</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>102</v>
+        <v>304</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>443</v>
+        <v>471</v>
       </c>
       <c r="AL94" t="s" s="2">
         <v>81</v>
@@ -13544,7 +13587,7 @@
         <v>81</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>444</v>
+        <v>472</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>81</v>
@@ -13552,12 +13595,14 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="C95" s="2"/>
+        <v>393</v>
+      </c>
+      <c r="C95" t="s" s="2">
+        <v>474</v>
+      </c>
       <c r="D95" t="s" s="2">
         <v>81</v>
       </c>
@@ -13578,18 +13623,20 @@
         <v>90</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>105</v>
+        <v>405</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>447</v>
+        <v>475</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>448</v>
+        <v>476</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="O95" s="2"/>
+        <v>397</v>
+      </c>
+      <c r="O95" t="s" s="2">
+        <v>398</v>
+      </c>
       <c r="P95" t="s" s="2">
         <v>81</v>
       </c>
@@ -13637,7 +13684,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>449</v>
+        <v>393</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -13652,16 +13699,16 @@
         <v>102</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>81</v>
+        <v>401</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>451</v>
+        <v>402</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>81</v>
@@ -13669,10 +13716,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>453</v>
+        <v>409</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13692,23 +13739,19 @@
         <v>81</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>299</v>
+        <v>105</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>454</v>
+        <v>106</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>456</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>81</v>
       </c>
@@ -13756,7 +13799,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>457</v>
+        <v>108</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -13765,13 +13808,13 @@
         <v>89</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>304</v>
+        <v>81</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>458</v>
+        <v>109</v>
       </c>
       <c r="AL96" t="s" s="2">
         <v>81</v>
@@ -13780,7 +13823,7 @@
         <v>81</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>459</v>
+        <v>81</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>81</v>
@@ -13788,14 +13831,14 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>479</v>
+        <v>411</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -13814,20 +13857,18 @@
         <v>81</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>480</v>
+        <v>112</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>481</v>
+        <v>113</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>482</v>
+        <v>114</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>484</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>81</v>
       </c>
@@ -13863,19 +13904,19 @@
         <v>81</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AC97" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AD97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>479</v>
+        <v>119</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13887,10 +13928,10 @@
         <v>101</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>485</v>
+        <v>120</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>486</v>
+        <v>103</v>
       </c>
       <c r="AL97" t="s" s="2">
         <v>81</v>
@@ -13899,7 +13940,7 @@
         <v>81</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>487</v>
+        <v>81</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>81</v>
@@ -13907,12 +13948,14 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="C98" s="2"/>
+        <v>411</v>
+      </c>
+      <c r="C98" t="s" s="2">
+        <v>480</v>
+      </c>
       <c r="D98" t="s" s="2">
         <v>81</v>
       </c>
@@ -13930,23 +13973,19 @@
         <v>81</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>173</v>
+        <v>481</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>492</v>
-      </c>
+        <v>483</v>
+      </c>
+      <c r="N98" s="2"/>
+      <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>81</v>
       </c>
@@ -13970,13 +14009,13 @@
         <v>81</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>267</v>
+        <v>81</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>493</v>
+        <v>81</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>494</v>
+        <v>81</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>81</v>
@@ -13994,31 +14033,31 @@
         <v>81</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>488</v>
+        <v>119</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>495</v>
+        <v>81</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>496</v>
+        <v>81</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>497</v>
+        <v>81</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>81</v>
@@ -14026,10 +14065,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>498</v>
+        <v>484</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>498</v>
+        <v>413</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14037,7 +14076,7 @@
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G99" t="s" s="2">
         <v>89</v>
@@ -14046,25 +14085,25 @@
         <v>81</v>
       </c>
       <c r="I99" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J99" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>499</v>
+        <v>173</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>500</v>
+        <v>414</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>501</v>
+        <v>415</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>502</v>
+        <v>416</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>503</v>
+        <v>417</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>81</v>
@@ -14074,7 +14113,7 @@
         <v>81</v>
       </c>
       <c r="S99" t="s" s="2">
-        <v>81</v>
+        <v>322</v>
       </c>
       <c r="T99" t="s" s="2">
         <v>81</v>
@@ -14089,13 +14128,13 @@
         <v>81</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>81</v>
+        <v>267</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>81</v>
+        <v>418</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>81</v>
+        <v>419</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>81</v>
@@ -14113,7 +14152,7 @@
         <v>81</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>498</v>
+        <v>420</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -14128,27 +14167,27 @@
         <v>102</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>504</v>
+        <v>421</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>505</v>
+        <v>81</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>506</v>
+        <v>422</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>507</v>
+        <v>81</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>508</v>
+        <v>485</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>508</v>
+        <v>424</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14165,25 +14204,25 @@
         <v>81</v>
       </c>
       <c r="I100" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J100" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>509</v>
+        <v>105</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>510</v>
+        <v>425</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>511</v>
+        <v>426</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>512</v>
+        <v>427</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>513</v>
+        <v>428</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>81</v>
@@ -14232,7 +14271,7 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>508</v>
+        <v>429</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -14247,16 +14286,16 @@
         <v>102</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>514</v>
+        <v>430</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>515</v>
+        <v>431</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>81</v>
@@ -14264,21 +14303,21 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>516</v>
+        <v>486</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>516</v>
+        <v>433</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>81</v>
+        <v>434</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>81</v>
@@ -14287,23 +14326,21 @@
         <v>81</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>237</v>
+        <v>105</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>238</v>
+        <v>435</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>239</v>
+        <v>436</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>517</v>
-      </c>
+        <v>437</v>
+      </c>
+      <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>81</v>
       </c>
@@ -14351,13 +14388,13 @@
         <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>516</v>
+        <v>438</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>101</v>
@@ -14366,7 +14403,7 @@
         <v>102</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>242</v>
+        <v>439</v>
       </c>
       <c r="AL101" t="s" s="2">
         <v>81</v>
@@ -14375,7 +14412,7 @@
         <v>81</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>243</v>
+        <v>440</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>81</v>
@@ -14383,21 +14420,21 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>518</v>
+        <v>487</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>518</v>
+        <v>442</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>81</v>
+        <v>443</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>81</v>
@@ -14406,23 +14443,21 @@
         <v>81</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>273</v>
+        <v>105</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>519</v>
+        <v>444</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>520</v>
+        <v>445</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>522</v>
-      </c>
+        <v>446</v>
+      </c>
+      <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>81</v>
       </c>
@@ -14446,11 +14481,13 @@
         <v>81</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y102" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z102" t="s" s="2">
-        <v>523</v>
+        <v>81</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>81</v>
@@ -14468,13 +14505,13 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>518</v>
+        <v>447</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>101</v>
@@ -14483,16 +14520,16 @@
         <v>102</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>524</v>
+        <v>448</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>525</v>
+        <v>81</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>526</v>
+        <v>449</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>81</v>
@@ -14500,10 +14537,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>527</v>
+        <v>488</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>527</v>
+        <v>451</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14514,7 +14551,7 @@
         <v>79</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>81</v>
@@ -14523,23 +14560,21 @@
         <v>81</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>528</v>
+        <v>105</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>529</v>
+        <v>452</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>530</v>
+        <v>453</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>532</v>
-      </c>
+        <v>454</v>
+      </c>
+      <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>81</v>
       </c>
@@ -14587,13 +14622,13 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>527</v>
+        <v>455</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>101</v>
@@ -14602,16 +14637,16 @@
         <v>102</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>533</v>
+        <v>456</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>534</v>
+        <v>457</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>81</v>
@@ -14619,10 +14654,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>535</v>
+        <v>489</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>535</v>
+        <v>459</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14642,23 +14677,21 @@
         <v>81</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>536</v>
+        <v>105</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>537</v>
+        <v>460</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>538</v>
+        <v>461</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>540</v>
-      </c>
+        <v>454</v>
+      </c>
+      <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>81</v>
       </c>
@@ -14706,7 +14739,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>535</v>
+        <v>462</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -14718,19 +14751,19 @@
         <v>101</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>541</v>
+        <v>102</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>542</v>
+        <v>463</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>543</v>
+        <v>464</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>81</v>
@@ -14738,10 +14771,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>544</v>
+        <v>490</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>544</v>
+        <v>466</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14752,7 +14785,7 @@
         <v>79</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>81</v>
@@ -14761,22 +14794,22 @@
         <v>81</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>545</v>
+        <v>299</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>546</v>
+        <v>467</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>547</v>
+        <v>468</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>548</v>
+        <v>302</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>549</v>
+        <v>469</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>81</v>
@@ -14825,31 +14858,31 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>544</v>
+        <v>470</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>550</v>
+        <v>304</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>551</v>
+        <v>471</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>81</v>
+        <v>472</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>81</v>
@@ -14857,10 +14890,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>552</v>
+        <v>491</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>552</v>
+        <v>491</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14871,7 +14904,7 @@
         <v>79</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>81</v>
@@ -14883,16 +14916,20 @@
         <v>81</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>105</v>
+        <v>492</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>106</v>
+        <v>493</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N106" s="2"/>
-      <c r="O106" s="2"/>
+        <v>494</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="O106" t="s" s="2">
+        <v>496</v>
+      </c>
       <c r="P106" t="s" s="2">
         <v>81</v>
       </c>
@@ -14940,22 +14977,22 @@
         <v>81</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>108</v>
+        <v>491</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>81</v>
+        <v>497</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>109</v>
+        <v>498</v>
       </c>
       <c r="AL106" t="s" s="2">
         <v>81</v>
@@ -14964,7 +15001,7 @@
         <v>81</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>81</v>
+        <v>499</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>81</v>
@@ -14972,21 +15009,21 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>553</v>
+        <v>500</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>553</v>
+        <v>500</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>81</v>
@@ -14995,21 +15032,23 @@
         <v>81</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>112</v>
+        <v>173</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>113</v>
+        <v>501</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>114</v>
+        <v>502</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O107" s="2"/>
+        <v>503</v>
+      </c>
+      <c r="O107" t="s" s="2">
+        <v>504</v>
+      </c>
       <c r="P107" t="s" s="2">
         <v>81</v>
       </c>
@@ -15033,55 +15072,55 @@
         <v>81</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>81</v>
+        <v>267</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>81</v>
+        <v>505</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>81</v>
+        <v>506</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AC107" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AD107" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>119</v>
+        <v>500</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>103</v>
+        <v>507</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>81</v>
+        <v>508</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>81</v>
+        <v>509</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>81</v>
@@ -15089,14 +15128,12 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>554</v>
+        <v>510</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="C108" t="s" s="2">
-        <v>555</v>
-      </c>
+        <v>510</v>
+      </c>
+      <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
         <v>81</v>
       </c>
@@ -15114,19 +15151,23 @@
         <v>81</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>556</v>
+        <v>511</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>557</v>
+        <v>512</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="N108" s="2"/>
-      <c r="O108" s="2"/>
+        <v>513</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="O108" t="s" s="2">
+        <v>515</v>
+      </c>
       <c r="P108" t="s" s="2">
         <v>81</v>
       </c>
@@ -15174,46 +15215,44 @@
         <v>81</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>119</v>
+        <v>510</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>81</v>
+        <v>516</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>81</v>
+        <v>517</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>81</v>
+        <v>518</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>81</v>
+        <v>519</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>559</v>
+        <v>520</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="C109" t="s" s="2">
-        <v>560</v>
-      </c>
+        <v>520</v>
+      </c>
+      <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
         <v>81</v>
       </c>
@@ -15228,22 +15267,26 @@
         <v>81</v>
       </c>
       <c r="I109" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>561</v>
+        <v>521</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>562</v>
+        <v>522</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="N109" s="2"/>
-      <c r="O109" s="2"/>
+        <v>523</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="O109" t="s" s="2">
+        <v>525</v>
+      </c>
       <c r="P109" t="s" s="2">
         <v>81</v>
       </c>
@@ -15291,31 +15334,31 @@
         <v>81</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>119</v>
+        <v>520</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>81</v>
+        <v>526</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>81</v>
+        <v>527</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>81</v>
@@ -15323,14 +15366,14 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>564</v>
+        <v>528</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>564</v>
+        <v>528</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>565</v>
+        <v>81</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -15343,25 +15386,25 @@
         <v>81</v>
       </c>
       <c r="I110" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>112</v>
+        <v>237</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>566</v>
+        <v>238</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>567</v>
+        <v>239</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>115</v>
+        <v>240</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>247</v>
+        <v>529</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>81</v>
@@ -15410,7 +15453,7 @@
         <v>81</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>568</v>
+        <v>528</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -15422,10 +15465,10 @@
         <v>101</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>103</v>
+        <v>242</v>
       </c>
       <c r="AL110" t="s" s="2">
         <v>81</v>
@@ -15434,7 +15477,7 @@
         <v>81</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>81</v>
+        <v>243</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>81</v>
@@ -15442,10 +15485,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>569</v>
+        <v>530</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>569</v>
+        <v>530</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15453,7 +15496,7 @@
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G111" t="s" s="2">
         <v>89</v>
@@ -15471,16 +15514,16 @@
         <v>273</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>570</v>
+        <v>531</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>571</v>
+        <v>532</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>521</v>
+        <v>533</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>572</v>
+        <v>534</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>81</v>
@@ -15507,33 +15550,33 @@
       <c r="X111" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="Y111" t="s" s="2">
-        <v>573</v>
-      </c>
+      <c r="Y111" s="2"/>
       <c r="Z111" t="s" s="2">
-        <v>574</v>
+        <v>535</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB111" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="AC111" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC111" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD111" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE111" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>569</v>
+        <v>530</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>101</v>
@@ -15542,16 +15585,16 @@
         <v>102</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>576</v>
+        <v>536</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>109</v>
+        <v>537</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>577</v>
+        <v>538</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>81</v>
@@ -15559,14 +15602,12 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>578</v>
+        <v>539</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="C112" t="s" s="2">
-        <v>579</v>
-      </c>
+        <v>539</v>
+      </c>
+      <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
         <v>81</v>
       </c>
@@ -15587,19 +15628,19 @@
         <v>81</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>273</v>
+        <v>540</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>580</v>
+        <v>541</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>571</v>
+        <v>542</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>521</v>
+        <v>543</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>572</v>
+        <v>544</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>81</v>
@@ -15624,11 +15665,13 @@
         <v>81</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y112" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z112" t="s" s="2">
-        <v>581</v>
+        <v>81</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>81</v>
@@ -15646,13 +15689,13 @@
         <v>81</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>569</v>
+        <v>539</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>101</v>
@@ -15661,7 +15704,7 @@
         <v>102</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>576</v>
+        <v>545</v>
       </c>
       <c r="AL112" t="s" s="2">
         <v>109</v>
@@ -15670,7 +15713,7 @@
         <v>81</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>577</v>
+        <v>546</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>81</v>
@@ -15678,14 +15721,12 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>582</v>
+        <v>547</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="C113" t="s" s="2">
-        <v>583</v>
-      </c>
+        <v>547</v>
+      </c>
+      <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
         <v>81</v>
       </c>
@@ -15694,7 +15735,7 @@
         <v>79</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>81</v>
@@ -15706,19 +15747,19 @@
         <v>81</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>273</v>
+        <v>548</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>584</v>
+        <v>549</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>571</v>
+        <v>550</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>521</v>
+        <v>551</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>572</v>
+        <v>552</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>81</v>
@@ -15743,11 +15784,13 @@
         <v>81</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y113" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y113" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z113" t="s" s="2">
-        <v>585</v>
+        <v>81</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>81</v>
@@ -15765,7 +15808,7 @@
         <v>81</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>569</v>
+        <v>547</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
@@ -15777,10 +15820,10 @@
         <v>101</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>102</v>
+        <v>553</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>576</v>
+        <v>554</v>
       </c>
       <c r="AL113" t="s" s="2">
         <v>109</v>
@@ -15789,7 +15832,7 @@
         <v>81</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>577</v>
+        <v>555</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>81</v>
@@ -15797,10 +15840,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>586</v>
+        <v>556</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>586</v>
+        <v>556</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15811,7 +15854,7 @@
         <v>79</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>81</v>
@@ -15823,19 +15866,19 @@
         <v>81</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>381</v>
+        <v>557</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>587</v>
+        <v>558</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>588</v>
+        <v>559</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>589</v>
+        <v>560</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>590</v>
+        <v>561</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>81</v>
@@ -15884,31 +15927,31 @@
         <v>81</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>586</v>
+        <v>556</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>102</v>
+        <v>562</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>591</v>
+        <v>563</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>592</v>
+        <v>81</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>81</v>
@@ -15916,10 +15959,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>593</v>
+        <v>564</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>593</v>
+        <v>564</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15930,7 +15973,7 @@
         <v>79</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>81</v>
@@ -15942,20 +15985,16 @@
         <v>81</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>480</v>
+        <v>105</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>481</v>
+        <v>106</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="O115" t="s" s="2">
-        <v>484</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N115" s="2"/>
+      <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
         <v>81</v>
       </c>
@@ -16003,22 +16042,22 @@
         <v>81</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>593</v>
+        <v>108</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>485</v>
+        <v>81</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>486</v>
+        <v>109</v>
       </c>
       <c r="AL115" t="s" s="2">
         <v>81</v>
@@ -16027,7 +16066,7 @@
         <v>81</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>487</v>
+        <v>81</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>81</v>
@@ -16035,21 +16074,21 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>595</v>
+        <v>565</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>595</v>
+        <v>565</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>81</v>
@@ -16061,20 +16100,18 @@
         <v>81</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>596</v>
+        <v>112</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>597</v>
+        <v>113</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>598</v>
+        <v>114</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="O116" t="s" s="2">
-        <v>599</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
         <v>81</v>
       </c>
@@ -16110,43 +16147,43 @@
         <v>81</v>
       </c>
       <c r="AB116" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AC116" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AD116" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE116" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>595</v>
+        <v>119</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI116" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>600</v>
+        <v>103</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>601</v>
+        <v>81</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>81</v>
@@ -16154,12 +16191,14 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>602</v>
+        <v>566</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="C117" s="2"/>
+        <v>565</v>
+      </c>
+      <c r="C117" t="s" s="2">
+        <v>567</v>
+      </c>
       <c r="D117" t="s" s="2">
         <v>81</v>
       </c>
@@ -16180,20 +16219,16 @@
         <v>81</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>173</v>
+        <v>568</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>489</v>
+        <v>569</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="O117" t="s" s="2">
-        <v>604</v>
-      </c>
+        <v>570</v>
+      </c>
+      <c r="N117" s="2"/>
+      <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
         <v>81</v>
       </c>
@@ -16217,13 +16252,13 @@
         <v>81</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>267</v>
+        <v>81</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>493</v>
+        <v>81</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>494</v>
+        <v>81</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>81</v>
@@ -16241,31 +16276,31 @@
         <v>81</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>602</v>
+        <v>119</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI117" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>495</v>
+        <v>81</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>605</v>
+        <v>81</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>81</v>
@@ -16273,12 +16308,14 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>606</v>
+        <v>571</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="C118" s="2"/>
+        <v>565</v>
+      </c>
+      <c r="C118" t="s" s="2">
+        <v>572</v>
+      </c>
       <c r="D118" t="s" s="2">
         <v>81</v>
       </c>
@@ -16299,20 +16336,16 @@
         <v>81</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>308</v>
+        <v>573</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>607</v>
+        <v>574</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="O118" t="s" s="2">
-        <v>610</v>
-      </c>
+        <v>575</v>
+      </c>
+      <c r="N118" s="2"/>
+      <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>81</v>
       </c>
@@ -16360,31 +16393,31 @@
         <v>81</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>606</v>
+        <v>119</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>611</v>
+        <v>101</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>313</v>
+        <v>120</v>
       </c>
       <c r="AK118" t="s" s="2">
-        <v>612</v>
+        <v>81</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="AM118" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>613</v>
+        <v>81</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>81</v>
@@ -16392,44 +16425,46 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>614</v>
+        <v>576</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>614</v>
+        <v>576</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>81</v>
+        <v>577</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H119" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I119" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>299</v>
+        <v>112</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>615</v>
+        <v>578</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>616</v>
+        <v>579</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="O119" s="2"/>
+        <v>115</v>
+      </c>
+      <c r="O119" t="s" s="2">
+        <v>247</v>
+      </c>
       <c r="P119" t="s" s="2">
         <v>81</v>
       </c>
@@ -16477,31 +16512,31 @@
         <v>81</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>614</v>
+        <v>580</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>304</v>
+        <v>120</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>617</v>
+        <v>103</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>618</v>
+        <v>81</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>81</v>
@@ -16509,10 +16544,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>619</v>
+        <v>581</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>619</v>
+        <v>581</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16520,10 +16555,10 @@
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H120" t="s" s="2">
         <v>81</v>
@@ -16535,19 +16570,19 @@
         <v>81</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>545</v>
+        <v>273</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>620</v>
+        <v>582</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>621</v>
+        <v>583</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>622</v>
+        <v>533</v>
       </c>
       <c r="O120" t="s" s="2">
-        <v>623</v>
+        <v>584</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>81</v>
@@ -16572,31 +16607,29 @@
         <v>81</v>
       </c>
       <c r="X120" t="s" s="2">
-        <v>81</v>
+        <v>153</v>
       </c>
       <c r="Y120" t="s" s="2">
-        <v>81</v>
+        <v>585</v>
       </c>
       <c r="Z120" t="s" s="2">
-        <v>81</v>
+        <v>586</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB120" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC120" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>587</v>
+      </c>
+      <c r="AC120" s="2"/>
       <c r="AD120" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE120" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>619</v>
+        <v>581</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -16611,16 +16644,16 @@
         <v>102</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>624</v>
+        <v>588</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>625</v>
+        <v>109</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>81</v>
+        <v>589</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>81</v>
@@ -16628,12 +16661,14 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>626</v>
+        <v>590</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="C121" s="2"/>
+        <v>581</v>
+      </c>
+      <c r="C121" t="s" s="2">
+        <v>591</v>
+      </c>
       <c r="D121" t="s" s="2">
         <v>81</v>
       </c>
@@ -16654,16 +16689,20 @@
         <v>81</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>105</v>
+        <v>273</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>106</v>
+        <v>592</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N121" s="2"/>
-      <c r="O121" s="2"/>
+        <v>583</v>
+      </c>
+      <c r="N121" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="O121" t="s" s="2">
+        <v>584</v>
+      </c>
       <c r="P121" t="s" s="2">
         <v>81</v>
       </c>
@@ -16687,13 +16726,11 @@
         <v>81</v>
       </c>
       <c r="X121" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y121" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="Y121" s="2"/>
       <c r="Z121" t="s" s="2">
-        <v>81</v>
+        <v>593</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>81</v>
@@ -16711,31 +16748,31 @@
         <v>81</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>108</v>
+        <v>581</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI121" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK121" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="AL121" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="AL121" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AM121" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>81</v>
+        <v>589</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>81</v>
@@ -16743,21 +16780,23 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>627</v>
+        <v>594</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="C122" s="2"/>
+        <v>581</v>
+      </c>
+      <c r="C122" t="s" s="2">
+        <v>595</v>
+      </c>
       <c r="D122" t="s" s="2">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G122" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H122" t="s" s="2">
         <v>81</v>
@@ -16769,18 +16808,20 @@
         <v>81</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>112</v>
+        <v>273</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>113</v>
+        <v>596</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>114</v>
+        <v>583</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O122" s="2"/>
+        <v>533</v>
+      </c>
+      <c r="O122" t="s" s="2">
+        <v>584</v>
+      </c>
       <c r="P122" t="s" s="2">
         <v>81</v>
       </c>
@@ -16804,31 +16845,29 @@
         <v>81</v>
       </c>
       <c r="X122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y122" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="Y122" s="2"/>
       <c r="Z122" t="s" s="2">
-        <v>81</v>
+        <v>597</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB122" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AC122" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AD122" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE122" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>119</v>
+        <v>581</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
@@ -16840,19 +16879,19 @@
         <v>101</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>103</v>
+        <v>588</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>81</v>
+        <v>589</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>81</v>
@@ -16860,45 +16899,45 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>628</v>
+        <v>598</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>628</v>
+        <v>598</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
-        <v>565</v>
+        <v>81</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H123" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I123" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J123" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>112</v>
+        <v>394</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>566</v>
+        <v>599</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>567</v>
+        <v>600</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>115</v>
+        <v>601</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>247</v>
+        <v>602</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>81</v>
@@ -16947,22 +16986,22 @@
         <v>81</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>568</v>
+        <v>598</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>103</v>
+        <v>603</v>
       </c>
       <c r="AL123" t="s" s="2">
         <v>81</v>
@@ -16971,7 +17010,7 @@
         <v>81</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>81</v>
+        <v>604</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>81</v>
@@ -16979,10 +17018,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>629</v>
+        <v>605</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>629</v>
+        <v>605</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16990,10 +17029,10 @@
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H124" t="s" s="2">
         <v>81</v>
@@ -17005,19 +17044,19 @@
         <v>81</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>273</v>
+        <v>492</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>630</v>
+        <v>493</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>631</v>
+        <v>494</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>632</v>
+        <v>606</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>633</v>
+        <v>496</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>81</v>
@@ -17042,13 +17081,13 @@
         <v>81</v>
       </c>
       <c r="X124" t="s" s="2">
-        <v>177</v>
+        <v>81</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>178</v>
+        <v>81</v>
       </c>
       <c r="Z124" t="s" s="2">
-        <v>179</v>
+        <v>81</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>81</v>
@@ -17066,31 +17105,31 @@
         <v>81</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>629</v>
+        <v>605</v>
       </c>
       <c r="AG124" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI124" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>102</v>
+        <v>497</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>634</v>
+        <v>498</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>635</v>
+        <v>81</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>636</v>
+        <v>499</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>81</v>
@@ -17098,10 +17137,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>637</v>
+        <v>607</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>637</v>
+        <v>607</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17124,19 +17163,19 @@
         <v>81</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>372</v>
+        <v>608</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>638</v>
+        <v>609</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>639</v>
+        <v>610</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>640</v>
+        <v>240</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>641</v>
+        <v>611</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>81</v>
@@ -17185,7 +17224,7 @@
         <v>81</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>637</v>
+        <v>607</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
@@ -17200,16 +17239,16 @@
         <v>102</v>
       </c>
       <c r="AK125" t="s" s="2">
-        <v>642</v>
+        <v>612</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>643</v>
+        <v>109</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>644</v>
+        <v>613</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>81</v>
@@ -17217,21 +17256,21 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>645</v>
+        <v>614</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>645</v>
+        <v>614</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
-        <v>646</v>
+        <v>81</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G126" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H126" t="s" s="2">
         <v>81</v>
@@ -17243,18 +17282,20 @@
         <v>81</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>647</v>
+        <v>173</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>648</v>
+        <v>501</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>649</v>
+        <v>615</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="O126" s="2"/>
+        <v>454</v>
+      </c>
+      <c r="O126" t="s" s="2">
+        <v>616</v>
+      </c>
       <c r="P126" t="s" s="2">
         <v>81</v>
       </c>
@@ -17278,13 +17319,13 @@
         <v>81</v>
       </c>
       <c r="X126" t="s" s="2">
-        <v>81</v>
+        <v>267</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>81</v>
+        <v>505</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>81</v>
+        <v>506</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>81</v>
@@ -17302,22 +17343,22 @@
         <v>81</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>645</v>
+        <v>614</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH126" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI126" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>313</v>
+        <v>102</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>651</v>
+        <v>507</v>
       </c>
       <c r="AL126" t="s" s="2">
         <v>109</v>
@@ -17326,7 +17367,7 @@
         <v>81</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>652</v>
+        <v>617</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>81</v>
@@ -17334,10 +17375,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>653</v>
+        <v>618</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>653</v>
+        <v>618</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17357,22 +17398,22 @@
         <v>81</v>
       </c>
       <c r="J127" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>654</v>
+        <v>308</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>655</v>
+        <v>619</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>656</v>
+        <v>620</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>657</v>
+        <v>621</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>658</v>
+        <v>622</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>81</v>
@@ -17421,7 +17462,7 @@
         <v>81</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>653</v>
+        <v>618</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
@@ -17430,22 +17471,22 @@
         <v>89</v>
       </c>
       <c r="AI127" t="s" s="2">
-        <v>101</v>
+        <v>623</v>
       </c>
       <c r="AJ127" t="s" s="2">
         <v>313</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>612</v>
+        <v>624</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>659</v>
+        <v>109</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>81</v>
+        <v>625</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>81</v>
@@ -17453,10 +17494,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>660</v>
+        <v>626</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>660</v>
+        <v>626</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17467,32 +17508,30 @@
         <v>79</v>
       </c>
       <c r="G128" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H128" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I128" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J128" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>545</v>
+        <v>299</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>661</v>
+        <v>627</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>662</v>
+        <v>628</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="O128" t="s" s="2">
-        <v>664</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
         <v>81</v>
       </c>
@@ -17540,22 +17579,22 @@
         <v>81</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>660</v>
+        <v>626</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH128" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI128" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>102</v>
+        <v>304</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>665</v>
+        <v>629</v>
       </c>
       <c r="AL128" t="s" s="2">
         <v>109</v>
@@ -17564,7 +17603,7 @@
         <v>81</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>81</v>
+        <v>630</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>81</v>
@@ -17572,10 +17611,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>666</v>
+        <v>631</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>666</v>
+        <v>631</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17586,7 +17625,7 @@
         <v>79</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H129" t="s" s="2">
         <v>81</v>
@@ -17598,16 +17637,20 @@
         <v>81</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>105</v>
+        <v>557</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>106</v>
+        <v>632</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N129" s="2"/>
-      <c r="O129" s="2"/>
+        <v>633</v>
+      </c>
+      <c r="N129" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="O129" t="s" s="2">
+        <v>635</v>
+      </c>
       <c r="P129" t="s" s="2">
         <v>81</v>
       </c>
@@ -17655,25 +17698,25 @@
         <v>81</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>108</v>
+        <v>631</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH129" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI129" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>109</v>
+        <v>636</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>81</v>
+        <v>637</v>
       </c>
       <c r="AM129" t="s" s="2">
         <v>81</v>
@@ -17687,21 +17730,21 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>667</v>
+        <v>638</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>667</v>
+        <v>638</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H130" t="s" s="2">
         <v>81</v>
@@ -17713,17 +17756,15 @@
         <v>81</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N130" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N130" s="2"/>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
         <v>81</v>
@@ -17760,34 +17801,34 @@
         <v>81</v>
       </c>
       <c r="AB130" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AC130" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AD130" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE130" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH130" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI130" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="AL130" t="s" s="2">
         <v>81</v>
@@ -17804,14 +17845,14 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>668</v>
+        <v>639</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>668</v>
+        <v>639</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>565</v>
+        <v>111</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
@@ -17824,26 +17865,24 @@
         <v>81</v>
       </c>
       <c r="I131" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J131" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K131" t="s" s="2">
         <v>112</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>566</v>
+        <v>113</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>567</v>
+        <v>114</v>
       </c>
       <c r="N131" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="O131" t="s" s="2">
-        <v>247</v>
-      </c>
+      <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
         <v>81</v>
       </c>
@@ -17879,19 +17918,19 @@
         <v>81</v>
       </c>
       <c r="AB131" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AC131" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AD131" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE131" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>568</v>
+        <v>119</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>79</v>
@@ -17923,44 +17962,46 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>669</v>
+        <v>640</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>669</v>
+        <v>640</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>81</v>
+        <v>577</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H132" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I132" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J132" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>670</v>
+        <v>112</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>671</v>
+        <v>578</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>672</v>
+        <v>579</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>673</v>
-      </c>
-      <c r="O132" s="2"/>
+        <v>115</v>
+      </c>
+      <c r="O132" t="s" s="2">
+        <v>247</v>
+      </c>
       <c r="P132" t="s" s="2">
         <v>81</v>
       </c>
@@ -18008,31 +18049,31 @@
         <v>81</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>669</v>
+        <v>580</v>
       </c>
       <c r="AG132" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH132" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI132" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ132" t="s" s="2">
-        <v>313</v>
+        <v>120</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>256</v>
+        <v>103</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="AM132" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>674</v>
+        <v>81</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>81</v>
@@ -18040,10 +18081,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>675</v>
+        <v>641</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>675</v>
+        <v>641</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18063,21 +18104,23 @@
         <v>81</v>
       </c>
       <c r="J133" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>173</v>
+        <v>273</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>676</v>
+        <v>642</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>677</v>
+        <v>643</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="O133" s="2"/>
+        <v>644</v>
+      </c>
+      <c r="O133" t="s" s="2">
+        <v>645</v>
+      </c>
       <c r="P133" t="s" s="2">
         <v>81</v>
       </c>
@@ -18101,13 +18144,13 @@
         <v>81</v>
       </c>
       <c r="X133" t="s" s="2">
-        <v>267</v>
+        <v>177</v>
       </c>
       <c r="Y133" t="s" s="2">
-        <v>677</v>
+        <v>178</v>
       </c>
       <c r="Z133" t="s" s="2">
-        <v>678</v>
+        <v>179</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>81</v>
@@ -18125,7 +18168,7 @@
         <v>81</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>675</v>
+        <v>641</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>89</v>
@@ -18140,18 +18183,1077 @@
         <v>102</v>
       </c>
       <c r="AK133" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="AL133" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="AM133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN133" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="AO133" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="C134" s="2"/>
+      <c r="D134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E134" s="2"/>
+      <c r="F134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G134" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K134" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="L134" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="M134" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="N134" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="O134" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="P134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q134" s="2"/>
+      <c r="R134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF134" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="AG134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH134" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI134" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ134" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK134" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="AL134" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="AM134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN134" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="AO134" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="B135" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="C135" s="2"/>
+      <c r="D135" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="E135" s="2"/>
+      <c r="F135" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K135" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="L135" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="M135" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="N135" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="O135" s="2"/>
+      <c r="P135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q135" s="2"/>
+      <c r="R135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF135" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="AG135" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI135" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ135" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AK135" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="AL135" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AM135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN135" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="AO135" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="B136" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="C136" s="2"/>
+      <c r="D136" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E136" s="2"/>
+      <c r="F136" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G136" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H136" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I136" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J136" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K136" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="L136" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="M136" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="N136" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="O136" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="P136" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q136" s="2"/>
+      <c r="R136" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S136" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T136" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U136" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V136" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W136" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X136" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y136" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z136" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA136" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB136" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC136" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD136" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE136" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF136" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="AG136" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH136" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI136" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ136" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AK136" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="AL136" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="AM136" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN136" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO136" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="B137" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="C137" s="2"/>
+      <c r="D137" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E137" s="2"/>
+      <c r="F137" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H137" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I137" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J137" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K137" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="L137" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="M137" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="N137" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="O137" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="P137" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q137" s="2"/>
+      <c r="R137" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S137" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T137" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U137" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V137" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W137" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X137" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y137" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z137" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA137" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB137" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC137" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD137" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE137" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF137" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="AG137" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI137" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ137" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK137" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="AL137" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AM137" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN137" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO137" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="B138" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="C138" s="2"/>
+      <c r="D138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E138" s="2"/>
+      <c r="F138" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G138" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K138" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L138" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M138" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="N138" s="2"/>
+      <c r="O138" s="2"/>
+      <c r="P138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q138" s="2"/>
+      <c r="R138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF138" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AG138" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH138" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK138" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AL138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO138" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s" s="2">
         <v>679</v>
       </c>
-      <c r="AL133" t="s" s="2">
+      <c r="B139" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="C139" s="2"/>
+      <c r="D139" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="E139" s="2"/>
+      <c r="F139" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G139" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H139" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I139" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J139" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K139" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L139" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="M139" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="N139" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O139" s="2"/>
+      <c r="P139" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q139" s="2"/>
+      <c r="R139" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S139" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T139" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U139" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V139" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W139" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X139" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y139" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z139" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA139" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB139" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AC139" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AD139" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE139" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AF139" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG139" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH139" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI139" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ139" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK139" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AL139" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM139" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN139" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO139" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="B140" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="C140" s="2"/>
+      <c r="D140" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="E140" s="2"/>
+      <c r="F140" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H140" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I140" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J140" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K140" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L140" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="M140" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="N140" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O140" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="P140" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q140" s="2"/>
+      <c r="R140" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S140" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T140" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U140" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V140" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W140" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X140" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y140" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z140" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA140" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB140" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC140" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD140" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE140" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF140" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="AG140" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI140" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ140" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK140" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AL140" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM140" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN140" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO140" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="B141" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="C141" s="2"/>
+      <c r="D141" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E141" s="2"/>
+      <c r="F141" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G141" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H141" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I141" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J141" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K141" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="L141" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="M141" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="N141" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="O141" s="2"/>
+      <c r="P141" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q141" s="2"/>
+      <c r="R141" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S141" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T141" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U141" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V141" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W141" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X141" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y141" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z141" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA141" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB141" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC141" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD141" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE141" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF141" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="AG141" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH141" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI141" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ141" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AK141" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AL141" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="AM133" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN133" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO133" t="s" s="2">
+      <c r="AM141" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN141" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="AO141" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="B142" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="C142" s="2"/>
+      <c r="D142" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E142" s="2"/>
+      <c r="F142" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G142" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H142" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I142" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J142" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K142" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="L142" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="M142" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="N142" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="O142" s="2"/>
+      <c r="P142" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q142" s="2"/>
+      <c r="R142" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S142" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T142" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U142" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V142" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W142" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X142" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="Y142" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="Z142" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="AA142" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB142" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC142" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD142" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE142" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF142" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="AG142" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH142" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI142" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ142" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK142" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="AL142" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AM142" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN142" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO142" t="s" s="2">
         <v>81</v>
       </c>
     </row>

--- a/ig/nr-update-patient-ins/StructureDefinition-fr-core-patient.xlsx
+++ b/ig/nr-update-patient-ins/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-26T11:06:19+00:00</t>
+    <t>2024-02-27T11:09:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-update-patient-ins/StructureDefinition-fr-core-patient.xlsx
+++ b/ig/nr-update-patient-ins/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-27T11:09:52+00:00</t>
+    <t>2024-02-27T11:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-update-patient-ins/StructureDefinition-fr-core-patient.xlsx
+++ b/ig/nr-update-patient-ins/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-27T11:11:58+00:00</t>
+    <t>2024-02-27T13:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
